--- a/spider2v-result.xlsx
+++ b/spider2v-result.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\projects\Spider2-V\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2D63EF9-ED2B-40ED-B86B-3D421C4D1446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{898E4613-3F93-4E7E-AFD2-9DD80F90634C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3380" yWindow="3380" windowWidth="16800" windowHeight="9670" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>coact_15_10_10_20</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -72,6 +72,10 @@
   </si>
   <si>
     <t>Tokens/M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>langgraph_gpt5_cua_50_summarize_rag_verbose</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -411,7 +415,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37.83203125" style="1" customWidth="1"/>
@@ -513,6 +517,20 @@
         <v>12.36</v>
       </c>
     </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="1">
+        <v>39.700000000000003</v>
+      </c>
+      <c r="C10" s="1">
+        <v>48.73</v>
+      </c>
+      <c r="D10" s="1">
+        <v>17.13</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
